--- a/data/trans_dic/P15D$nada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,87; 48,42</t>
+          <t>11,69; 47,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 30,33</t>
+          <t>10,68; 30,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 31,77</t>
+          <t>8,78; 31,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 31,34</t>
+          <t>8,2; 28,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,44</t>
+          <t>0,0; 33,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,47; 38,77</t>
+          <t>13,82; 38,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 19,41</t>
+          <t>2,0; 18,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 26,73</t>
+          <t>10,81; 26,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 33,62</t>
+          <t>9,82; 35,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,5; 30,72</t>
+          <t>15,03; 30,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 20,83</t>
+          <t>6,92; 21,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,65; 25,15</t>
+          <t>11,71; 25,85</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 28,65</t>
+          <t>5,09; 28,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,83; 33,99</t>
+          <t>13,93; 32,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 25,78</t>
+          <t>6,24; 23,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 34,69</t>
+          <t>11,72; 35,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,25; 44,48</t>
+          <t>12,72; 47,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,53; 35,82</t>
+          <t>15,33; 36,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,27; 33,98</t>
+          <t>9,19; 31,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 38,24</t>
+          <t>13,95; 36,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 30,54</t>
+          <t>11,11; 29,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,01; 30,74</t>
+          <t>16,09; 30,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 23,98</t>
+          <t>9,64; 23,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,99; 31,42</t>
+          <t>14,83; 30,69</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,57; 58,7</t>
+          <t>20,16; 59,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 29,57</t>
+          <t>9,77; 29,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 33,08</t>
+          <t>5,83; 32,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 34,62</t>
+          <t>3,75; 33,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 29,31</t>
+          <t>3,83; 29,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,87; 36,4</t>
+          <t>13,83; 37,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,06; 45,66</t>
+          <t>13,22; 47,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 28,77</t>
+          <t>8,75; 28,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,71; 38,51</t>
+          <t>12,89; 37,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,31; 30,25</t>
+          <t>13,93; 29,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,29; 34,25</t>
+          <t>12,68; 34,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,14; 25,14</t>
+          <t>8,78; 25,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,42; 53,32</t>
+          <t>18,75; 52,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,14; 45,79</t>
+          <t>25,06; 46,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 31,22</t>
+          <t>9,29; 30,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 22,34</t>
+          <t>6,28; 22,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 30,57</t>
+          <t>3,85; 30,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,79; 50,05</t>
+          <t>26,31; 49,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,38</t>
+          <t>2,12; 20,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,59; 27,55</t>
+          <t>13,28; 27,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 38,79</t>
+          <t>14,56; 38,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,21; 44,65</t>
+          <t>28,55; 44,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 21,17</t>
+          <t>7,34; 21,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 22,26</t>
+          <t>11,71; 22,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,7; 36,19</t>
+          <t>18,6; 34,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,5; 30,95</t>
+          <t>19,99; 30,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 22,02</t>
+          <t>11,44; 22,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,56; 23,56</t>
+          <t>11,69; 23,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 24,85</t>
+          <t>9,93; 25,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,3; 34,01</t>
+          <t>22,37; 34,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 20,55</t>
+          <t>9,48; 20,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,21; 24,68</t>
+          <t>15,48; 24,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,24; 28,3</t>
+          <t>16,9; 28,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,1; 30,95</t>
+          <t>22,83; 30,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,28</t>
+          <t>11,93; 19,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,66; 22,03</t>
+          <t>14,81; 22,01</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tuvo consecuencias el último accidente</t>
+          <t>Población que no tuvo consecuencias el último accidente (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2705; 11032</t>
+          <t>2663; 10750</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6189; 17899</t>
+          <t>6305; 17898</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3596; 13220</t>
+          <t>3652; 13080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3823; 14067</t>
+          <t>3681; 12895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5306</t>
+          <t>0; 5343</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7596; 20347</t>
+          <t>7254; 20284</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>976; 9448</t>
+          <t>972; 8799</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4402; 11559</t>
+          <t>4676; 11506</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3653; 12992</t>
+          <t>3795; 13800</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17278; 34251</t>
+          <t>16761; 34482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6313; 18808</t>
+          <t>6249; 18971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10270; 22165</t>
+          <t>10316; 22783</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2161; 12256</t>
+          <t>2179; 11992</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10940; 26877</t>
+          <t>11018; 25770</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3690; 15593</t>
+          <t>3771; 14349</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7655; 23261</t>
+          <t>7862; 23628</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3693; 13404</t>
+          <t>3832; 14462</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10543; 25985</t>
+          <t>11120; 26501</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4870; 16108</t>
+          <t>4358; 15133</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8224; 21886</t>
+          <t>7983; 20981</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8385; 22269</t>
+          <t>8100; 21730</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25786; 46615</t>
+          <t>24401; 46557</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10675; 25867</t>
+          <t>10404; 25738</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18633; 39053</t>
+          <t>18428; 38147</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4658; 13974</t>
+          <t>4800; 14053</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5511; 16991</t>
+          <t>5611; 16975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2126; 12131</t>
+          <t>2139; 11791</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1322; 10122</t>
+          <t>1097; 9901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>917; 7067</t>
+          <t>923; 7217</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7914; 20762</t>
+          <t>7887; 21167</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4121; 14410</t>
+          <t>4173; 15056</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3783; 12688</t>
+          <t>3859; 12732</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6571; 18452</t>
+          <t>6177; 18036</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16384; 34642</t>
+          <t>15951; 33479</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8388; 23371</t>
+          <t>8650; 23539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6705; 18439</t>
+          <t>6437; 18523</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6548; 17973</t>
+          <t>6320; 17528</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23061; 40392</t>
+          <t>22101; 41315</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6066; 19008</t>
+          <t>5658; 18319</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3430; 13154</t>
+          <t>3698; 13050</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>900; 7241</t>
+          <t>912; 7217</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19368; 36182</t>
+          <t>19015; 35721</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1338; 12763</t>
+          <t>1328; 12997</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9376; 19017</t>
+          <t>9165; 18703</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8593; 22266</t>
+          <t>8356; 21850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46879; 71654</t>
+          <t>45821; 71528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8882; 26143</t>
+          <t>9062; 26491</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14929; 28472</t>
+          <t>14983; 28546</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24250; 44542</t>
+          <t>22894; 42545</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>58173; 87817</t>
+          <t>56722; 87176</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22072; 43968</t>
+          <t>22845; 44501</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23136; 47135</t>
+          <t>23395; 46013</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9594; 23310</t>
+          <t>9318; 23607</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56707; 86513</t>
+          <t>56893; 87597</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17651; 39101</t>
+          <t>18046; 38099</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32488; 52725</t>
+          <t>33063; 52911</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37386; 61372</t>
+          <t>36652; 60982</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124316; 166554</t>
+          <t>122858; 162758</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46506; 75176</t>
+          <t>46519; 74381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>60643; 91146</t>
+          <t>61252; 91050</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$nada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15D$nada-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,69; 47,19</t>
+          <t>11,04; 46,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 30,32</t>
+          <t>10,71; 30,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 31,44</t>
+          <t>8,8; 31,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 28,73</t>
+          <t>7,59; 29,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,67</t>
+          <t>0,0; 30,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,82; 38,65</t>
+          <t>13,86; 39,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 18,08</t>
+          <t>2,05; 18,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 26,61</t>
+          <t>10,41; 25,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,82; 35,71</t>
+          <t>9,28; 35,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 30,93</t>
+          <t>15,74; 31,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 21,01</t>
+          <t>7,21; 20,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 25,85</t>
+          <t>10,69; 23,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 28,03</t>
+          <t>6,95; 30,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,93; 32,59</t>
+          <t>14,0; 34,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 23,73</t>
+          <t>6,04; 24,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 35,23</t>
+          <t>9,8; 30,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,72; 47,99</t>
+          <t>12,32; 47,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,33; 36,53</t>
+          <t>15,19; 36,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 31,92</t>
+          <t>8,84; 33,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,95; 36,66</t>
+          <t>13,67; 34,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,11; 29,8</t>
+          <t>11,31; 30,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,09; 30,71</t>
+          <t>17,15; 31,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 23,86</t>
+          <t>9,94; 23,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 30,69</t>
+          <t>12,75; 27,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,16; 59,03</t>
+          <t>19,55; 56,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 29,54</t>
+          <t>9,87; 30,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 32,16</t>
+          <t>5,74; 32,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 33,87</t>
+          <t>3,01; 28,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 29,93</t>
+          <t>3,89; 30,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 37,11</t>
+          <t>13,35; 36,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 47,71</t>
+          <t>13,31; 46,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 28,87</t>
+          <t>8,16; 25,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,89; 37,64</t>
+          <t>14,27; 38,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,93; 29,24</t>
+          <t>14,13; 29,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 34,5</t>
+          <t>12,48; 33,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 25,26</t>
+          <t>8,54; 22,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 52,0</t>
+          <t>18,52; 51,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,06; 46,84</t>
+          <t>26,18; 47,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 30,09</t>
+          <t>9,52; 31,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 22,16</t>
+          <t>6,88; 23,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 30,46</t>
+          <t>0,0; 31,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,31; 49,42</t>
+          <t>26,13; 50,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 20,76</t>
+          <t>2,73; 24,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 27,1</t>
+          <t>12,72; 26,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 38,07</t>
+          <t>14,88; 38,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,55; 44,57</t>
+          <t>29,38; 45,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 21,45</t>
+          <t>7,85; 20,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,71; 22,32</t>
+          <t>11,7; 22,71</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,6; 34,57</t>
+          <t>18,72; 34,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,99; 30,72</t>
+          <t>19,97; 30,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,44; 22,29</t>
+          <t>11,67; 22,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,69; 23,0</t>
+          <t>11,09; 21,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,93; 25,17</t>
+          <t>10,6; 25,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,37; 34,44</t>
+          <t>22,94; 34,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,48; 20,02</t>
+          <t>9,54; 19,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,48; 24,77</t>
+          <t>14,46; 22,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,9; 28,12</t>
+          <t>16,71; 28,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,83; 30,25</t>
+          <t>22,87; 30,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,08</t>
+          <t>11,7; 19,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,81; 22,01</t>
+          <t>14,12; 20,41</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15506</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2663; 10750</t>
+          <t>2515; 10558</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6305; 17898</t>
+          <t>6320; 18028</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3652; 13080</t>
+          <t>3662; 13104</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3681; 12895</t>
+          <t>3772; 14408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5343</t>
+          <t>0; 4893</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7254; 20284</t>
+          <t>7272; 20534</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>972; 8799</t>
+          <t>998; 9094</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4676; 11506</t>
+          <t>4884; 11817</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3795; 13800</t>
+          <t>3587; 13532</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16761; 34482</t>
+          <t>17550; 35036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6249; 18971</t>
+          <t>6514; 18735</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10316; 22783</t>
+          <t>10327; 22750</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>26858</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2179; 11992</t>
+          <t>2975; 12905</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11018; 25770</t>
+          <t>11073; 27575</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3771; 14349</t>
+          <t>3655; 14815</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7862; 23628</t>
+          <t>7334; 22638</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3832; 14462</t>
+          <t>3712; 14382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11120; 26501</t>
+          <t>11019; 26356</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4358; 15133</t>
+          <t>4191; 15841</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7983; 20981</t>
+          <t>8587; 21765</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8100; 21730</t>
+          <t>8248; 22543</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24401; 46557</t>
+          <t>26005; 47430</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10404; 25738</t>
+          <t>10727; 25269</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18428; 38147</t>
+          <t>17551; 37306</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11781</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4800; 14053</t>
+          <t>4653; 13564</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5611; 16975</t>
+          <t>5670; 17563</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2139; 11791</t>
+          <t>2105; 11972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1097; 9901</t>
+          <t>994; 9309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>923; 7217</t>
+          <t>938; 7258</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7887; 21167</t>
+          <t>7616; 20652</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4173; 15056</t>
+          <t>4202; 14602</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3859; 12732</t>
+          <t>4038; 12695</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6177; 18036</t>
+          <t>6838; 18682</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15951; 33479</t>
+          <t>16178; 33810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8650; 23539</t>
+          <t>8513; 22915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6437; 18523</t>
+          <t>7045; 18902</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>22616</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6320; 17528</t>
+          <t>6242; 17323</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22101; 41315</t>
+          <t>23089; 41665</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5658; 18319</t>
+          <t>5794; 19218</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3698; 13050</t>
+          <t>4369; 14914</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>912; 7217</t>
+          <t>0; 7475</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19015; 35721</t>
+          <t>18886; 36347</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1328; 12997</t>
+          <t>1711; 15488</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9165; 18703</t>
+          <t>9285; 19651</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8356; 21850</t>
+          <t>8544; 22348</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45821; 71528</t>
+          <t>47153; 72388</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9062; 26491</t>
+          <t>9698; 25248</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14983; 28546</t>
+          <t>15975; 30999</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>42901</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>76762</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22894; 42545</t>
+          <t>23046; 42555</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56722; 87176</t>
+          <t>56671; 86248</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22845; 44501</t>
+          <t>23303; 44783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23395; 46013</t>
+          <t>24518; 46864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9318; 23607</t>
+          <t>9943; 24120</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56893; 87597</t>
+          <t>58345; 87992</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18046; 38099</t>
+          <t>18150; 37960</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33063; 52911</t>
+          <t>33584; 52788</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36652; 60982</t>
+          <t>36241; 61094</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>122858; 162758</t>
+          <t>123051; 165548</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46519; 74381</t>
+          <t>45605; 74175</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61252; 91050</t>
+          <t>63985; 92485</t>
         </is>
       </c>
     </row>
